--- a/CAN_WB_timeseries.xlsx
+++ b/CAN_WB_timeseries.xlsx
@@ -14,21 +14,111 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>Bank capital to assets ratio (%)</t>
+  </si>
+  <si>
+    <t>Bank liquid reserves to bank assets (%)</t>
+  </si>
+  <si>
+    <t>Bank nonperforming loans (% of gross loans)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Debt (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government revenue (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
     <t>Interest payments (% of GDP)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Net lending/borrowing (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
     <t>Tax revenue (% of GDP)</t>
   </si>
   <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -389,12 +479,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AJ26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:36">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -411,502 +501,2641 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:36">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="E2">
+        <v>2.04931902885437</v>
+      </c>
+      <c r="F2">
+        <v>2.48322832733607</v>
+      </c>
+      <c r="G2">
+        <v>58.7379742383571</v>
+      </c>
+      <c r="H2">
+        <v>73.987738492292</v>
+      </c>
+      <c r="I2">
+        <v>44.209235821106</v>
+      </c>
+      <c r="J2">
         <v>5.1385391803606</v>
       </c>
-      <c r="C2">
+      <c r="K2">
+        <v>29362.0841609786</v>
+      </c>
+      <c r="L2">
+        <v>24271.0020563821</v>
+      </c>
+      <c r="M2">
+        <v>4.16394849476771</v>
+      </c>
+      <c r="N2">
+        <v>33.4</v>
+      </c>
+      <c r="O2">
+        <v>1.84907865524292</v>
+      </c>
+      <c r="P2">
+        <v>19.1064161806335</v>
+      </c>
+      <c r="Q2">
+        <v>18.7745182688509</v>
+      </c>
+      <c r="R2">
+        <v>20.8617411485603</v>
+      </c>
+      <c r="S2">
+        <v>38.5561220292153</v>
+      </c>
+      <c r="T2">
         <v>2.71943995691976</v>
       </c>
-      <c r="D2">
+      <c r="U2">
         <v>21.9717034739813</v>
       </c>
-      <c r="E2">
+      <c r="V2">
+        <v>79.1668292682927</v>
+      </c>
+      <c r="W2">
+        <v>1.11434980213748</v>
+      </c>
+      <c r="X2">
+        <v>2.19246100809809</v>
+      </c>
+      <c r="Y2">
+        <v>1.16752684116364</v>
+      </c>
+      <c r="Z2">
+        <v>30685730</v>
+      </c>
+      <c r="AA2">
+        <v>0.2</v>
+      </c>
+      <c r="AB2">
+        <v>1.46447455883026</v>
+      </c>
+      <c r="AC2">
+        <v>1.66548609733582</v>
+      </c>
+      <c r="AD2">
         <v>14.8577431846106</v>
       </c>
-      <c r="F2">
+      <c r="AE2">
+        <v>32427268296.4522</v>
+      </c>
+      <c r="AF2">
+        <v>1.16129866637947</v>
+      </c>
+      <c r="AG2">
+        <v>82.76535785032139</v>
+      </c>
+      <c r="AH2">
         <v>6.829</v>
       </c>
+      <c r="AI2">
+        <v>79.47799999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>1.53196537494659</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:36">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>0.393560139524134</v>
+      </c>
+      <c r="F3">
+        <v>2.13236979231819</v>
+      </c>
+      <c r="G3">
+        <v>57.4583564504362</v>
+      </c>
+      <c r="H3">
+        <v>121.35283176137</v>
+      </c>
+      <c r="I3">
+        <v>42.0399550909321</v>
+      </c>
+      <c r="J3">
         <v>1.87509810696022</v>
       </c>
-      <c r="C3">
+      <c r="K3">
+        <v>30230.8487685762</v>
+      </c>
+      <c r="L3">
+        <v>23822.096210932</v>
+      </c>
+      <c r="M3">
+        <v>0.774519407466116</v>
+      </c>
+      <c r="N3">
+        <v>33.6</v>
+      </c>
+      <c r="P3">
+        <v>19.5093203790186</v>
+      </c>
+      <c r="Q3">
+        <v>18.7110049059225</v>
+      </c>
+      <c r="R3">
+        <v>20.1601523762926</v>
+      </c>
+      <c r="S3">
+        <v>36.3042633034376</v>
+      </c>
+      <c r="T3">
         <v>2.52512013979906</v>
       </c>
-      <c r="D3">
+      <c r="U3">
         <v>19.6923709106531</v>
       </c>
-      <c r="E3">
+      <c r="V3">
+        <v>79.3980487804878</v>
+      </c>
+      <c r="W3">
+        <v>1.13335628281332</v>
+      </c>
+      <c r="X3">
+        <v>1.6407536685204</v>
+      </c>
+      <c r="Z3">
+        <v>31020855</v>
+      </c>
+      <c r="AA3">
+        <v>0.2</v>
+      </c>
+      <c r="AD3">
         <v>14.1814798149467</v>
       </c>
-      <c r="F3">
+      <c r="AE3">
+        <v>34252695467.5387</v>
+      </c>
+      <c r="AF3">
+        <v>1.31951370457923</v>
+      </c>
+      <c r="AG3">
+        <v>78.3442183943698</v>
+      </c>
+      <c r="AH3">
         <v>7.219</v>
       </c>
+      <c r="AI3">
+        <v>79.81</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:36">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="C4">
+        <v>0.370909678513256</v>
+      </c>
+      <c r="E4">
+        <v>1.98223149776459</v>
+      </c>
+      <c r="F4">
+        <v>1.64503032397306</v>
+      </c>
+      <c r="G4">
+        <v>54.1491194927984</v>
+      </c>
+      <c r="H4">
+        <v>117.839456406914</v>
+      </c>
+      <c r="I4">
+        <v>40.0586585930818</v>
+      </c>
+      <c r="J4">
         <v>2.99925535017809</v>
       </c>
-      <c r="C4">
+      <c r="K4">
+        <v>30963.9218856684</v>
+      </c>
+      <c r="L4">
+        <v>24256.0192337185</v>
+      </c>
+      <c r="M4">
+        <v>1.88796484648248</v>
+      </c>
+      <c r="N4">
+        <v>33.6</v>
+      </c>
+      <c r="O4">
+        <v>1.86085593700409</v>
+      </c>
+      <c r="P4">
+        <v>19.7787192119877</v>
+      </c>
+      <c r="Q4">
+        <v>17.963084125068</v>
+      </c>
+      <c r="R4">
+        <v>19.3246638356621</v>
+      </c>
+      <c r="S4">
+        <v>35.6483734848415</v>
+      </c>
+      <c r="T4">
         <v>2.25839440940855</v>
       </c>
-      <c r="D4">
+      <c r="U4">
         <v>17.3059793025935</v>
       </c>
-      <c r="E4">
+      <c r="V4">
+        <v>79.5307317073171</v>
+      </c>
+      <c r="W4">
+        <v>1.11686914736943</v>
+      </c>
+      <c r="X4">
+        <v>1.47509355467556</v>
+      </c>
+      <c r="Y4">
+        <v>1.21803176403046</v>
+      </c>
+      <c r="Z4">
+        <v>31359199</v>
+      </c>
+      <c r="AA4">
+        <v>0.2</v>
+      </c>
+      <c r="AB4">
+        <v>1.53391695022583</v>
+      </c>
+      <c r="AC4">
+        <v>1.66139602661133</v>
+      </c>
+      <c r="AD4">
         <v>13.3776274685072</v>
       </c>
-      <c r="F4">
+      <c r="AE4">
+        <v>37189390323.6644</v>
+      </c>
+      <c r="AF4">
+        <v>1.4362408296048</v>
+      </c>
+      <c r="AG4">
+        <v>75.7070320779233</v>
+      </c>
+      <c r="AH4">
         <v>7.665</v>
       </c>
+      <c r="AI4">
+        <v>79.88800000000001</v>
+      </c>
+      <c r="AJ4">
+        <v>1.49905383586884</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:36">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>0.313276167839908</v>
+      </c>
+      <c r="E5">
+        <v>1.93129205703735</v>
+      </c>
+      <c r="F5">
+        <v>1.16498813828327</v>
+      </c>
+      <c r="G5">
+        <v>51.2713370557453</v>
+      </c>
+      <c r="H5">
+        <v>113.240980376842</v>
+      </c>
+      <c r="I5">
+        <v>36.8659851985508</v>
+      </c>
+      <c r="J5">
         <v>1.80638512302554</v>
       </c>
-      <c r="C5">
+      <c r="K5">
+        <v>32351.5456968698</v>
+      </c>
+      <c r="L5">
+        <v>28301.8645937428</v>
+      </c>
+      <c r="M5">
+        <v>0.89501858100094</v>
+      </c>
+      <c r="N5">
+        <v>33.8</v>
+      </c>
+      <c r="O5">
+        <v>1.92467999458313</v>
+      </c>
+      <c r="P5">
+        <v>19.8962017689692</v>
+      </c>
+      <c r="Q5">
+        <v>18.0373335713637</v>
+      </c>
+      <c r="R5">
+        <v>19.0651145813243</v>
+      </c>
+      <c r="S5">
+        <v>32.9741094185099</v>
+      </c>
+      <c r="T5">
         <v>2.75856321360112</v>
       </c>
-      <c r="D5">
+      <c r="U5">
         <v>15.6975459743198</v>
       </c>
-      <c r="E5">
+      <c r="V5">
+        <v>79.7151219512195</v>
+      </c>
+      <c r="W5">
+        <v>1.11193730688338</v>
+      </c>
+      <c r="X5">
+        <v>1.10596441340132</v>
+      </c>
+      <c r="Y5">
+        <v>1.05307674407959</v>
+      </c>
+      <c r="Z5">
+        <v>31642461</v>
+      </c>
+      <c r="AA5">
+        <v>0.2</v>
+      </c>
+      <c r="AB5">
+        <v>1.52460896968842</v>
+      </c>
+      <c r="AC5">
+        <v>1.69705653190613</v>
+      </c>
+      <c r="AD5">
         <v>13.2289347132717</v>
       </c>
-      <c r="F5">
+      <c r="AE5">
+        <v>36267581049.3034</v>
+      </c>
+      <c r="AF5">
+        <v>1.28132010174152</v>
+      </c>
+      <c r="AG5">
+        <v>69.8400946170607</v>
+      </c>
+      <c r="AH5">
         <v>7.574</v>
       </c>
+      <c r="AI5">
+        <v>79.967</v>
+      </c>
+      <c r="AJ5">
+        <v>1.54755675792694</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:36">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <v>0.309264149242815</v>
+      </c>
+      <c r="E6">
+        <v>1.80586624145508</v>
+      </c>
+      <c r="F6">
+        <v>2.26315076447856</v>
+      </c>
+      <c r="G6">
+        <v>46.8009858324025</v>
+      </c>
+      <c r="H6">
+        <v>115.443313139541</v>
+      </c>
+      <c r="I6">
+        <v>37.3277713060483</v>
+      </c>
+      <c r="J6">
         <v>3.09236384292251</v>
       </c>
-      <c r="C6">
+      <c r="K6">
+        <v>33927.6696952532</v>
+      </c>
+      <c r="L6">
+        <v>32145.5412620217</v>
+      </c>
+      <c r="M6">
+        <v>2.13581560192544</v>
+      </c>
+      <c r="N6">
+        <v>33.8</v>
+      </c>
+      <c r="O6">
+        <v>1.90069770812988</v>
+      </c>
+      <c r="P6">
+        <v>19.4174844503805</v>
+      </c>
+      <c r="Q6">
+        <v>17.2659172104417</v>
+      </c>
+      <c r="R6">
+        <v>18.6903132683099</v>
+      </c>
+      <c r="S6">
+        <v>32.864648684908</v>
+      </c>
+      <c r="T6">
         <v>1.85725871857256</v>
       </c>
-      <c r="D6">
+      <c r="U6">
         <v>14.6592953929539</v>
       </c>
-      <c r="E6">
+      <c r="V6">
+        <v>79.9921951219512</v>
+      </c>
+      <c r="W6">
+        <v>1.10418939142687</v>
+      </c>
+      <c r="X6">
+        <v>1.49185011274784</v>
+      </c>
+      <c r="Y6">
+        <v>0.87644749879837</v>
+      </c>
+      <c r="Z6">
+        <v>31938807</v>
+      </c>
+      <c r="AA6">
+        <v>0.2</v>
+      </c>
+      <c r="AB6">
+        <v>1.61642110347748</v>
+      </c>
+      <c r="AC6">
+        <v>1.68714725971222</v>
+      </c>
+      <c r="AD6">
         <v>13.3447478670743</v>
       </c>
-      <c r="F6">
+      <c r="AE6">
+        <v>34476385087.8754</v>
+      </c>
+      <c r="AF6">
+        <v>1.06751407941516</v>
+      </c>
+      <c r="AG6">
+        <v>70.1924199909562</v>
+      </c>
+      <c r="AH6">
         <v>7.185</v>
       </c>
+      <c r="AI6">
+        <v>80.045</v>
+      </c>
+      <c r="AJ6">
+        <v>1.66845452785492</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:36">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
+        <v>4.50904265128511</v>
+      </c>
+      <c r="C7">
+        <v>0.282653270708232</v>
+      </c>
+      <c r="D7">
+        <v>0.499517649324799</v>
+      </c>
+      <c r="E7">
+        <v>1.86970067024231</v>
+      </c>
+      <c r="F7">
+        <v>1.86965618692433</v>
+      </c>
+      <c r="G7">
+        <v>46.0616514241618</v>
+      </c>
+      <c r="H7">
+        <v>121.661092958293</v>
+      </c>
+      <c r="I7">
+        <v>36.8567073235071</v>
+      </c>
+      <c r="J7">
         <v>3.21045439063563</v>
       </c>
-      <c r="C7">
+      <c r="K7">
+        <v>36328.378994377</v>
+      </c>
+      <c r="L7">
+        <v>36383.6600068095</v>
+      </c>
+      <c r="M7">
+        <v>2.23757661617552</v>
+      </c>
+      <c r="N7">
+        <v>33.6</v>
+      </c>
+      <c r="O7">
+        <v>1.88245940208435</v>
+      </c>
+      <c r="P7">
+        <v>19.0759109803014</v>
+      </c>
+      <c r="Q7">
+        <v>17.8239879344923</v>
+      </c>
+      <c r="R7">
+        <v>18.52968507421</v>
+      </c>
+      <c r="S7">
+        <v>32.9024256932286</v>
+      </c>
+      <c r="T7">
         <v>2.21355203439768</v>
       </c>
-      <c r="D7">
+      <c r="U7">
         <v>12.8135100895489</v>
       </c>
-      <c r="E7">
+      <c r="V7">
+        <v>80.11268292682929</v>
+      </c>
+      <c r="W7">
+        <v>1.10710542420811</v>
+      </c>
+      <c r="X7">
+        <v>0.743050128273399</v>
+      </c>
+      <c r="Y7">
+        <v>0.828725039958954</v>
+      </c>
+      <c r="Z7">
+        <v>32242732</v>
+      </c>
+      <c r="AA7">
+        <v>0.2</v>
+      </c>
+      <c r="AB7">
+        <v>1.56574976444244</v>
+      </c>
+      <c r="AC7">
+        <v>1.65014719963074</v>
+      </c>
+      <c r="AD7">
         <v>13.2994928856977</v>
       </c>
-      <c r="F7">
+      <c r="AE7">
+        <v>33018041276.077</v>
+      </c>
+      <c r="AF7">
+        <v>0.883794061681326</v>
+      </c>
+      <c r="AG7">
+        <v>69.7591330167357</v>
+      </c>
+      <c r="AH7">
         <v>6.758</v>
       </c>
+      <c r="AI7">
+        <v>80.122</v>
+      </c>
+      <c r="AJ7">
+        <v>1.50687944889069</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:36">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
+        <v>4.58166993633633</v>
+      </c>
+      <c r="C8">
+        <v>0.281399600324914</v>
+      </c>
+      <c r="D8">
+        <v>0.420325955427002</v>
+      </c>
+      <c r="E8">
+        <v>1.95279455184937</v>
+      </c>
+      <c r="F8">
+        <v>1.36365624553912</v>
+      </c>
+      <c r="G8">
+        <v>43.2916781929928</v>
+      </c>
+      <c r="H8">
+        <v>134.12080712347</v>
+      </c>
+      <c r="I8">
+        <v>35.4024592168513</v>
+      </c>
+      <c r="J8">
         <v>2.63794375007348</v>
       </c>
-      <c r="C8">
+      <c r="K8">
+        <v>38119.3909593545</v>
+      </c>
+      <c r="L8">
+        <v>40504.0370977806</v>
+      </c>
+      <c r="M8">
+        <v>1.60290147691838</v>
+      </c>
+      <c r="N8">
+        <v>34.1</v>
+      </c>
+      <c r="O8">
+        <v>1.89211332798004</v>
+      </c>
+      <c r="P8">
+        <v>19.2487641773811</v>
+      </c>
+      <c r="Q8">
+        <v>17.0276912468077</v>
+      </c>
+      <c r="R8">
+        <v>18.5317932825239</v>
+      </c>
+      <c r="S8">
+        <v>32.6497052601475</v>
+      </c>
+      <c r="T8">
         <v>2.00202539534162</v>
       </c>
-      <c r="D8">
+      <c r="U8">
         <v>12.7648803917875</v>
       </c>
-      <c r="E8">
+      <c r="V8">
+        <v>80.5436585365854</v>
+      </c>
+      <c r="W8">
+        <v>1.12252472932052</v>
+      </c>
+      <c r="X8">
+        <v>1.53203249555318</v>
+      </c>
+      <c r="Y8">
+        <v>1.03495657444</v>
+      </c>
+      <c r="Z8">
+        <v>32571193</v>
+      </c>
+      <c r="AA8">
+        <v>0.2</v>
+      </c>
+      <c r="AB8">
+        <v>1.55865693092346</v>
+      </c>
+      <c r="AC8">
+        <v>1.80108332633972</v>
+      </c>
+      <c r="AD8">
         <v>13.3482206693421</v>
       </c>
-      <c r="F8">
+      <c r="AE8">
+        <v>35063091947.1937</v>
+      </c>
+      <c r="AF8">
+        <v>0.83462996521452</v>
+      </c>
+      <c r="AG8">
+        <v>68.0521644769988</v>
+      </c>
+      <c r="AH8">
         <v>6.484</v>
       </c>
+      <c r="AI8">
+        <v>80.21299999999999</v>
+      </c>
+      <c r="AJ8">
+        <v>1.41559481620789</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:36">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
+        <v>4.22304366211909</v>
+      </c>
+      <c r="C9">
+        <v>0.306311200351619</v>
+      </c>
+      <c r="D9">
+        <v>0.431596614050767</v>
+      </c>
+      <c r="E9">
+        <v>1.99088037014008</v>
+      </c>
+      <c r="F9">
+        <v>0.752359497275173</v>
+      </c>
+      <c r="G9">
+        <v>39.1585639491399</v>
+      </c>
+      <c r="H9">
+        <v>123.533648061052</v>
+      </c>
+      <c r="I9">
+        <v>34.229555163977</v>
+      </c>
+      <c r="J9">
         <v>2.04990463726786</v>
       </c>
-      <c r="C9">
+      <c r="K9">
+        <v>39575.4770075876</v>
+      </c>
+      <c r="L9">
+        <v>44660.0838892281</v>
+      </c>
+      <c r="M9">
+        <v>1.06414487775739</v>
+      </c>
+      <c r="N9">
+        <v>33.8</v>
+      </c>
+      <c r="O9">
+        <v>1.75481534004211</v>
+      </c>
+      <c r="P9">
+        <v>19.2505356033619</v>
+      </c>
+      <c r="Q9">
+        <v>16.9627803202211</v>
+      </c>
+      <c r="R9">
+        <v>18.6951561172876</v>
+      </c>
+      <c r="S9">
+        <v>32.0538645842577</v>
+      </c>
+      <c r="T9">
         <v>2.13838399266837</v>
       </c>
-      <c r="D9">
+      <c r="U9">
         <v>11.9320665881957</v>
       </c>
-      <c r="E9">
+      <c r="V9">
+        <v>80.5436585365854</v>
+      </c>
+      <c r="W9">
+        <v>1.18579022996702</v>
+      </c>
+      <c r="X9">
+        <v>1.78676013843287</v>
+      </c>
+      <c r="Y9">
+        <v>1.00701069831848</v>
+      </c>
+      <c r="Z9">
+        <v>32888886</v>
+      </c>
+      <c r="AA9">
+        <v>0.2</v>
+      </c>
+      <c r="AB9">
+        <v>1.60638952255249</v>
+      </c>
+      <c r="AC9">
+        <v>1.79710018634796</v>
+      </c>
+      <c r="AD9">
         <v>13.3344320068963</v>
       </c>
-      <c r="F9">
+      <c r="AE9">
+        <v>41082108778.8237</v>
+      </c>
+      <c r="AF9">
+        <v>0.878669443792734</v>
+      </c>
+      <c r="AG9">
+        <v>66.28341974823471</v>
+      </c>
+      <c r="AH9">
         <v>6.156</v>
       </c>
+      <c r="AI9">
+        <v>80.396</v>
+      </c>
+      <c r="AJ9">
+        <v>1.38467156887054</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:36">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
+        <v>4.0461602097785</v>
+      </c>
+      <c r="C10">
+        <v>0.229613786156668</v>
+      </c>
+      <c r="D10">
+        <v>0.763250457412455</v>
+      </c>
+      <c r="E10">
+        <v>1.98772144317627</v>
+      </c>
+      <c r="F10">
+        <v>0.204634001322009</v>
+      </c>
+      <c r="G10">
+        <v>45.3205112731135</v>
+      </c>
+      <c r="H10">
+        <v>124.097771689277</v>
+      </c>
+      <c r="I10">
+        <v>34.3950055520687</v>
+      </c>
+      <c r="J10">
         <v>0.995406301140747</v>
       </c>
-      <c r="C10">
+      <c r="K10">
+        <v>40376.0882836384</v>
+      </c>
+      <c r="L10">
+        <v>46710.2526864484</v>
+      </c>
+      <c r="M10">
+        <v>-0.0933427924909864</v>
+      </c>
+      <c r="N10">
+        <v>33.9</v>
+      </c>
+      <c r="O10">
+        <v>1.78248238563538</v>
+      </c>
+      <c r="P10">
+        <v>19.7194394824506</v>
+      </c>
+      <c r="Q10">
+        <v>17.0833534495245</v>
+      </c>
+      <c r="R10">
+        <v>17.6208781924395</v>
+      </c>
+      <c r="S10">
+        <v>32.6286028098296</v>
+      </c>
+      <c r="T10">
         <v>2.37027067444298</v>
       </c>
-      <c r="D10">
+      <c r="U10">
         <v>10.8256381633331</v>
       </c>
-      <c r="E10">
+      <c r="V10">
+        <v>80.7246341463415</v>
+      </c>
+      <c r="W10">
+        <v>1.24551836677548</v>
+      </c>
+      <c r="X10">
+        <v>0.777651716313426</v>
+      </c>
+      <c r="Y10">
+        <v>1.0413726568222</v>
+      </c>
+      <c r="Z10">
+        <v>33247298</v>
+      </c>
+      <c r="AA10">
+        <v>0.2</v>
+      </c>
+      <c r="AB10">
+        <v>1.65094351768494</v>
+      </c>
+      <c r="AC10">
+        <v>1.79639303684235</v>
+      </c>
+      <c r="AD10">
         <v>12.3901655964853</v>
       </c>
-      <c r="F10">
+      <c r="AE10">
+        <v>43872316563.9077</v>
+      </c>
+      <c r="AF10">
+        <v>0.881536944156731</v>
+      </c>
+      <c r="AG10">
+        <v>67.0236083618983</v>
+      </c>
+      <c r="AH10">
         <v>6.284</v>
       </c>
+      <c r="AI10">
+        <v>80.578</v>
+      </c>
+      <c r="AJ10">
+        <v>1.40752851963043</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:36">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
+        <v>4.75623982302236</v>
+      </c>
+      <c r="D11">
+        <v>1.26687055816181</v>
+      </c>
+      <c r="E11">
+        <v>2.05179667472839</v>
+      </c>
+      <c r="F11">
+        <v>-2.96628242314574</v>
+      </c>
+      <c r="G11">
+        <v>53.1924466726998</v>
+      </c>
+      <c r="I11">
+        <v>28.5158343165743</v>
+      </c>
+      <c r="J11">
         <v>-2.91508621550267</v>
       </c>
-      <c r="C11">
+      <c r="K11">
+        <v>38864.0566958538</v>
+      </c>
+      <c r="L11">
+        <v>40874.8831932903</v>
+      </c>
+      <c r="M11">
+        <v>-4.02008809742583</v>
+      </c>
+      <c r="N11">
+        <v>34</v>
+      </c>
+      <c r="O11">
+        <v>1.74208331108093</v>
+      </c>
+      <c r="P11">
+        <v>21.9645855050549</v>
+      </c>
+      <c r="Q11">
+        <v>18.85417104193</v>
+      </c>
+      <c r="R11">
+        <v>17.6435436387172</v>
+      </c>
+      <c r="S11">
+        <v>29.9585575059154</v>
+      </c>
+      <c r="T11">
         <v>0.299466803009305</v>
       </c>
-      <c r="D11">
+      <c r="U11">
         <v>9.350844860292581</v>
       </c>
-      <c r="E11">
+      <c r="V11">
+        <v>81.06609756097561</v>
+      </c>
+      <c r="W11">
+        <v>1.37755563107525</v>
+      </c>
+      <c r="X11">
+        <v>-1.2041997436573</v>
+      </c>
+      <c r="Y11">
+        <v>1.12707591056824</v>
+      </c>
+      <c r="Z11">
+        <v>33630069</v>
+      </c>
+      <c r="AA11">
+        <v>0.2</v>
+      </c>
+      <c r="AB11">
+        <v>1.69657874107361</v>
+      </c>
+      <c r="AC11">
+        <v>1.7967267036438</v>
+      </c>
+      <c r="AD11">
         <v>12.3043859548638</v>
       </c>
-      <c r="F11">
+      <c r="AE11">
+        <v>54356329766.8962</v>
+      </c>
+      <c r="AF11">
+        <v>1.36080788737442</v>
+      </c>
+      <c r="AG11">
+        <v>58.4743918224897</v>
+      </c>
+      <c r="AH11">
         <v>8.460000000000001</v>
       </c>
+      <c r="AI11">
+        <v>80.758</v>
+      </c>
+      <c r="AJ11">
+        <v>1.40189552307129</v>
+      </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:36">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
+        <v>4.76631113956</v>
+      </c>
+      <c r="D12">
+        <v>1.19245724160614</v>
+      </c>
+      <c r="E12">
+        <v>2.06187319755554</v>
+      </c>
+      <c r="F12">
+        <v>-3.59618567149688</v>
+      </c>
+      <c r="G12">
+        <v>53.1497329605545</v>
+      </c>
+      <c r="I12">
+        <v>29.1673819330319</v>
+      </c>
+      <c r="J12">
         <v>3.09080634469335</v>
       </c>
-      <c r="C12">
+      <c r="K12">
+        <v>40098.2537191139</v>
+      </c>
+      <c r="L12">
+        <v>47560.6666009406</v>
+      </c>
+      <c r="M12">
+        <v>1.95144744690714</v>
+      </c>
+      <c r="N12">
+        <v>33.6</v>
+      </c>
+      <c r="O12">
+        <v>1.77782678604126</v>
+      </c>
+      <c r="P12">
+        <v>21.4754574603582</v>
+      </c>
+      <c r="Q12">
+        <v>19.0847071449408</v>
+      </c>
+      <c r="R12">
+        <v>16.8961721345029</v>
+      </c>
+      <c r="S12">
+        <v>31.0407395714164</v>
+      </c>
+      <c r="T12">
         <v>1.77687154092627</v>
       </c>
-      <c r="D12">
+      <c r="U12">
         <v>8.89420052836835</v>
       </c>
-      <c r="E12">
+      <c r="V12">
+        <v>81.3221951219512</v>
+      </c>
+      <c r="W12">
+        <v>1.19433833839121</v>
+      </c>
+      <c r="X12">
+        <v>-2.22136723715912</v>
+      </c>
+      <c r="Y12">
+        <v>0.936318218708038</v>
+      </c>
+      <c r="Z12">
+        <v>34005902</v>
+      </c>
+      <c r="AA12">
+        <v>0.2</v>
+      </c>
+      <c r="AB12">
+        <v>1.69343030452728</v>
+      </c>
+      <c r="AC12">
+        <v>1.79859042167664</v>
+      </c>
+      <c r="AD12">
         <v>11.7328092981826</v>
       </c>
-      <c r="F12">
+      <c r="AE12">
+        <v>57151157771.2186</v>
+      </c>
+      <c r="AF12">
+        <v>1.17295270117455</v>
+      </c>
+      <c r="AG12">
+        <v>60.2081215044483</v>
+      </c>
+      <c r="AH12">
         <v>8.178000000000001</v>
       </c>
+      <c r="AI12">
+        <v>80.937</v>
+      </c>
+      <c r="AJ12">
+        <v>1.35265874862671</v>
+      </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:36">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
+        <v>4.87671555885921</v>
+      </c>
+      <c r="D13">
+        <v>0.844688790542748</v>
+      </c>
+      <c r="E13">
+        <v>1.97113347053528</v>
+      </c>
+      <c r="F13">
+        <v>-2.77400602599856</v>
+      </c>
+      <c r="G13">
+        <v>54.1193858391726</v>
+      </c>
+      <c r="I13">
+        <v>30.6783919173107</v>
+      </c>
+      <c r="J13">
         <v>3.13719442170364</v>
       </c>
-      <c r="C13">
+      <c r="K13">
+        <v>41666.8374590278</v>
+      </c>
+      <c r="L13">
+        <v>52223.8588398531</v>
+      </c>
+      <c r="M13">
+        <v>2.13607717133128</v>
+      </c>
+      <c r="N13">
+        <v>32.7</v>
+      </c>
+      <c r="O13">
+        <v>1.77254545688629</v>
+      </c>
+      <c r="P13">
+        <v>21.1458668604215</v>
+      </c>
+      <c r="Q13">
+        <v>17.8502680006291</v>
+      </c>
+      <c r="R13">
+        <v>16.9254981361992</v>
+      </c>
+      <c r="S13">
+        <v>31.8203468535221</v>
+      </c>
+      <c r="T13">
         <v>2.91213508872347</v>
       </c>
-      <c r="D13">
+      <c r="U13">
         <v>9.116602194679089</v>
       </c>
-      <c r="E13">
+      <c r="V13">
+        <v>81.4826829268293</v>
+      </c>
+      <c r="W13">
+        <v>1.19329189549638</v>
+      </c>
+      <c r="X13">
+        <v>-0.911072492915979</v>
+      </c>
+      <c r="Y13">
+        <v>1.07717573642731</v>
+      </c>
+      <c r="Z13">
+        <v>34339221</v>
+      </c>
+      <c r="AA13">
+        <v>0.2</v>
+      </c>
+      <c r="AB13">
+        <v>1.68484020233154</v>
+      </c>
+      <c r="AC13">
+        <v>1.72711992263794</v>
+      </c>
+      <c r="AD13">
         <v>11.8039212812623</v>
       </c>
-      <c r="F13">
+      <c r="AE13">
+        <v>65818985667.1989</v>
+      </c>
+      <c r="AF13">
+        <v>1.19116603863505</v>
+      </c>
+      <c r="AG13">
+        <v>62.4987387708328</v>
+      </c>
+      <c r="AH13">
         <v>7.637</v>
       </c>
+      <c r="AI13">
+        <v>81.096</v>
+      </c>
+      <c r="AJ13">
+        <v>1.38014459609985</v>
+      </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:36">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
+        <v>4.61982973068852</v>
+      </c>
+      <c r="D14">
+        <v>0.651152891186439</v>
+      </c>
+      <c r="E14">
+        <v>1.91890442371368</v>
+      </c>
+      <c r="F14">
+        <v>-3.53224767688727</v>
+      </c>
+      <c r="G14">
+        <v>55.7251649377054</v>
+      </c>
+      <c r="I14">
+        <v>30.3530255225878</v>
+      </c>
+      <c r="J14">
         <v>1.75566129145483</v>
       </c>
-      <c r="C14">
+      <c r="K14">
+        <v>42291.9729357094</v>
+      </c>
+      <c r="L14">
+        <v>52670.3447335415</v>
+      </c>
+      <c r="M14">
+        <v>0.658841956783917</v>
+      </c>
+      <c r="N14">
+        <v>33.5</v>
+      </c>
+      <c r="O14">
+        <v>1.75697004795074</v>
+      </c>
+      <c r="P14">
+        <v>21.0578451788387</v>
+      </c>
+      <c r="Q14">
+        <v>17.5175199279774</v>
+      </c>
+      <c r="R14">
+        <v>16.9203236637378</v>
+      </c>
+      <c r="S14">
+        <v>32.2425234169127</v>
+      </c>
+      <c r="T14">
         <v>1.51567823124525</v>
       </c>
-      <c r="D14">
+      <c r="U14">
         <v>8.53971338504941</v>
       </c>
-      <c r="E14">
+      <c r="V14">
+        <v>81.6636585365854</v>
+      </c>
+      <c r="W14">
+        <v>1.11840459807104</v>
+      </c>
+      <c r="X14">
+        <v>-0.516854977958138</v>
+      </c>
+      <c r="Y14">
+        <v>1.11301624774933</v>
+      </c>
+      <c r="Z14">
+        <v>34713395</v>
+      </c>
+      <c r="AA14">
+        <v>0.2</v>
+      </c>
+      <c r="AB14">
+        <v>1.70719468593597</v>
+      </c>
+      <c r="AC14">
+        <v>1.75642120838165</v>
+      </c>
+      <c r="AD14">
         <v>11.6644273631038</v>
       </c>
-      <c r="F14">
+      <c r="AE14">
+        <v>68546343361.9693</v>
+      </c>
+      <c r="AF14">
+        <v>1.19486014225825</v>
+      </c>
+      <c r="AG14">
+        <v>62.5955489395005</v>
+      </c>
+      <c r="AH14">
         <v>7.392</v>
       </c>
+      <c r="AI14">
+        <v>81.137</v>
+      </c>
+      <c r="AJ14">
+        <v>1.43750536441803</v>
+      </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:36">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
+        <v>4.30271410755344</v>
+      </c>
+      <c r="D15">
+        <v>0.5749181961487529</v>
+      </c>
+      <c r="E15">
+        <v>1.87937796115875</v>
+      </c>
+      <c r="F15">
+        <v>-3.14687545091254</v>
+      </c>
+      <c r="G15">
+        <v>53.200869076551</v>
+      </c>
+      <c r="I15">
+        <v>30.3319386683867</v>
+      </c>
+      <c r="J15">
         <v>2.32581354806429</v>
       </c>
-      <c r="C15">
+      <c r="K15">
+        <v>44301.0562529133</v>
+      </c>
+      <c r="L15">
+        <v>52638.1187235237</v>
+      </c>
+      <c r="M15">
+        <v>1.2535901034471</v>
+      </c>
+      <c r="N15">
+        <v>33.8</v>
+      </c>
+      <c r="O15">
+        <v>1.78074109554291</v>
+      </c>
+      <c r="P15">
+        <v>20.7043347111761</v>
+      </c>
+      <c r="Q15">
+        <v>17.0848821579089</v>
+      </c>
+      <c r="R15">
+        <v>16.9526176646696</v>
+      </c>
+      <c r="S15">
+        <v>31.8991362329537</v>
+      </c>
+      <c r="T15">
         <v>0.938291897815245</v>
       </c>
-      <c r="D15">
+      <c r="U15">
         <v>8.397000587697731</v>
       </c>
-      <c r="E15">
+      <c r="V15">
+        <v>81.74487804878051</v>
+      </c>
+      <c r="W15">
+        <v>1.00236720047397</v>
+      </c>
+      <c r="X15">
+        <v>-0.0719674448508055</v>
+      </c>
+      <c r="Y15">
+        <v>1.06142175197601</v>
+      </c>
+      <c r="Z15">
+        <v>35080992</v>
+      </c>
+      <c r="AA15">
+        <v>0.5</v>
+      </c>
+      <c r="AB15">
+        <v>1.72989094257355</v>
+      </c>
+      <c r="AC15">
+        <v>1.74750757217407</v>
+      </c>
+      <c r="AD15">
         <v>11.6235045990299</v>
       </c>
-      <c r="F15">
+      <c r="AE15">
+        <v>71937085415.7952</v>
+      </c>
+      <c r="AF15">
+        <v>1.2551770449071</v>
+      </c>
+      <c r="AG15">
+        <v>62.2310749013405</v>
+      </c>
+      <c r="AH15">
         <v>7.143</v>
       </c>
+      <c r="AI15">
+        <v>81.178</v>
+      </c>
+      <c r="AJ15">
+        <v>1.45344030857086</v>
+      </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:36">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
+        <v>4.4783876783578</v>
+      </c>
+      <c r="D16">
+        <v>0.517878594833065</v>
+      </c>
+      <c r="E16">
+        <v>1.83219265937805</v>
+      </c>
+      <c r="F16">
+        <v>-2.31892137730875</v>
+      </c>
+      <c r="G16">
+        <v>51.4827081297932</v>
+      </c>
+      <c r="I16">
+        <v>31.7365758733408</v>
+      </c>
+      <c r="J16">
         <v>2.87346677785811</v>
       </c>
-      <c r="C16">
+      <c r="K16">
+        <v>45758.1007297304</v>
+      </c>
+      <c r="L16">
+        <v>50960.8431174661</v>
+      </c>
+      <c r="M16">
+        <v>1.84840952337521</v>
+      </c>
+      <c r="N16">
+        <v>33.2</v>
+      </c>
+      <c r="O16">
+        <v>1.75371766090393</v>
+      </c>
+      <c r="P16">
+        <v>20.266560128167</v>
+      </c>
+      <c r="Q16">
+        <v>16.4020498301416</v>
+      </c>
+      <c r="R16">
+        <v>16.9792224861735</v>
+      </c>
+      <c r="S16">
+        <v>32.6420862831515</v>
+      </c>
+      <c r="T16">
         <v>1.90663590717867</v>
       </c>
-      <c r="D16">
+      <c r="U16">
         <v>7.70589601594113</v>
       </c>
-      <c r="E16">
+      <c r="V16">
+        <v>81.78439024390249</v>
+      </c>
+      <c r="W16">
+        <v>0.989925299438869</v>
+      </c>
+      <c r="X16">
+        <v>0.948871044469965</v>
+      </c>
+      <c r="Y16">
+        <v>1.17550384998322</v>
+      </c>
+      <c r="Z16">
+        <v>35434066</v>
+      </c>
+      <c r="AA16">
+        <v>0.2</v>
+      </c>
+      <c r="AB16">
+        <v>1.83872532844543</v>
+      </c>
+      <c r="AC16">
+        <v>1.88629722595215</v>
+      </c>
+      <c r="AD16">
         <v>11.8083790792206</v>
       </c>
-      <c r="F16">
+      <c r="AE16">
+        <v>74699962252.5789</v>
+      </c>
+      <c r="AF16">
+        <v>1.29918684137955</v>
+      </c>
+      <c r="AG16">
+        <v>64.3786621564923</v>
+      </c>
+      <c r="AH16">
         <v>7.023</v>
       </c>
+      <c r="AI16">
+        <v>81.218</v>
+      </c>
+      <c r="AJ16">
+        <v>1.41233158111572</v>
+      </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:36">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
+        <v>4.55248540735644</v>
+      </c>
+      <c r="D17">
+        <v>0.516596294246744</v>
+      </c>
+      <c r="E17">
+        <v>1.84565019607544</v>
+      </c>
+      <c r="F17">
+        <v>-3.51398716666025</v>
+      </c>
+      <c r="G17">
+        <v>55.9915837788793</v>
+      </c>
+      <c r="I17">
+        <v>31.8499609634443</v>
+      </c>
+      <c r="J17">
         <v>0.649971001734855</v>
       </c>
-      <c r="C17">
+      <c r="K17">
+        <v>44669.4513631838</v>
+      </c>
+      <c r="L17">
+        <v>43594.1941045394</v>
+      </c>
+      <c r="M17">
+        <v>-0.11236916498423</v>
+      </c>
+      <c r="N17">
+        <v>33.7</v>
+      </c>
+      <c r="O17">
+        <v>1.7309353351593</v>
+      </c>
+      <c r="P17">
+        <v>20.8778251262785</v>
+      </c>
+      <c r="Q17">
+        <v>17.0597786823228</v>
+      </c>
+      <c r="R17">
+        <v>17.8509094964837</v>
+      </c>
+      <c r="S17">
+        <v>34.3149411035338</v>
+      </c>
+      <c r="T17">
         <v>1.12524136094278</v>
       </c>
-      <c r="D17">
+      <c r="U17">
         <v>7.01250128841312</v>
       </c>
-      <c r="E17">
+      <c r="V17">
+        <v>81.8258536585366</v>
+      </c>
+      <c r="W17">
+        <v>1.15270937445521</v>
+      </c>
+      <c r="X17">
+        <v>0.9987228967234409</v>
+      </c>
+      <c r="Y17">
+        <v>1.26233685016632</v>
+      </c>
+      <c r="Z17">
+        <v>35704498</v>
+      </c>
+      <c r="AA17">
+        <v>0.5</v>
+      </c>
+      <c r="AB17">
+        <v>1.70605802536011</v>
+      </c>
+      <c r="AC17">
+        <v>1.8071414232254</v>
+      </c>
+      <c r="AD17">
         <v>12.3898109063213</v>
       </c>
-      <c r="F17">
+      <c r="AE17">
+        <v>79753521149.89931</v>
+      </c>
+      <c r="AF17">
+        <v>1.5439294501743</v>
+      </c>
+      <c r="AG17">
+        <v>66.1649020669781</v>
+      </c>
+      <c r="AH17">
         <v>6.945</v>
       </c>
+      <c r="AI17">
+        <v>81.259</v>
+      </c>
+      <c r="AJ17">
+        <v>1.46729922294617</v>
+      </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:36">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
+        <v>4.65117202502206</v>
+      </c>
+      <c r="D18">
+        <v>0.596050944805398</v>
+      </c>
+      <c r="E18">
+        <v>1.94446551799774</v>
+      </c>
+      <c r="F18">
+        <v>-3.093111446907</v>
+      </c>
+      <c r="G18">
+        <v>56.0236243991088</v>
+      </c>
+      <c r="I18">
+        <v>31.5025724093362</v>
+      </c>
+      <c r="J18">
         <v>1.03855092490855</v>
       </c>
-      <c r="C18">
+      <c r="K18">
+        <v>46470.6466391109</v>
+      </c>
+      <c r="L18">
+        <v>42314.0615817218</v>
+      </c>
+      <c r="M18">
+        <v>-0.0982963624127819</v>
+      </c>
+      <c r="N18">
+        <v>32.7</v>
+      </c>
+      <c r="O18">
+        <v>1.7445410490036</v>
+      </c>
+      <c r="P18">
+        <v>21.0480401948524</v>
+      </c>
+      <c r="Q18">
+        <v>17.498604071126</v>
+      </c>
+      <c r="R18">
+        <v>17.8650755134574</v>
+      </c>
+      <c r="S18">
+        <v>33.8611121122194</v>
+      </c>
+      <c r="T18">
         <v>1.42875954701085</v>
       </c>
-      <c r="D18">
+      <c r="U18">
         <v>6.3601737952827</v>
       </c>
-      <c r="E18">
+      <c r="V18">
+        <v>81.94</v>
+      </c>
+      <c r="W18">
+        <v>1.16416156719089</v>
+      </c>
+      <c r="X18">
+        <v>0.412730871331151</v>
+      </c>
+      <c r="Y18">
+        <v>1.24041163921356</v>
+      </c>
+      <c r="Z18">
+        <v>36110803</v>
+      </c>
+      <c r="AA18">
+        <v>0.5</v>
+      </c>
+      <c r="AB18">
+        <v>1.72741413116455</v>
+      </c>
+      <c r="AC18">
+        <v>1.8009147644043</v>
+      </c>
+      <c r="AD18">
         <v>12.496562633144</v>
       </c>
-      <c r="F18">
+      <c r="AE18">
+        <v>82718110857.6299</v>
+      </c>
+      <c r="AF18">
+        <v>1.65079590323093</v>
+      </c>
+      <c r="AG18">
+        <v>65.3636845215556</v>
+      </c>
+      <c r="AH18">
         <v>7.038</v>
       </c>
+      <c r="AI18">
+        <v>81.3</v>
+      </c>
+      <c r="AJ18">
+        <v>1.44561123847961</v>
+      </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:36">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
+        <v>4.79472477595189</v>
+      </c>
+      <c r="D19">
+        <v>0.449461039885323</v>
+      </c>
+      <c r="E19">
+        <v>1.88144600391388</v>
+      </c>
+      <c r="F19">
+        <v>-2.8034274767599</v>
+      </c>
+      <c r="G19">
+        <v>54.4625651849142</v>
+      </c>
+      <c r="I19">
+        <v>31.4544101509781</v>
+      </c>
+      <c r="J19">
         <v>3.03383491200222</v>
       </c>
-      <c r="C19">
+      <c r="K19">
+        <v>48317.3874457163</v>
+      </c>
+      <c r="L19">
+        <v>45129.628116623</v>
+      </c>
+      <c r="M19">
+        <v>1.8094644720755</v>
+      </c>
+      <c r="N19">
+        <v>33.3</v>
+      </c>
+      <c r="O19">
+        <v>1.81557297706604</v>
+      </c>
+      <c r="P19">
+        <v>20.7033313853187</v>
+      </c>
+      <c r="Q19">
+        <v>17.6065954076372</v>
+      </c>
+      <c r="R19">
+        <v>18.0104464036707</v>
+      </c>
+      <c r="S19">
+        <v>33.6466506994867</v>
+      </c>
+      <c r="T19">
         <v>1.5968841285297</v>
       </c>
-      <c r="D19">
+      <c r="U19">
         <v>5.87167744777046</v>
       </c>
-      <c r="E19">
+      <c r="V19">
+        <v>81.81292682926831</v>
+      </c>
+      <c r="W19">
+        <v>1.35189646465708</v>
+      </c>
+      <c r="X19">
+        <v>0.439587955196598</v>
+      </c>
+      <c r="Y19">
+        <v>1.08968114852905</v>
+      </c>
+      <c r="Z19">
+        <v>36545075</v>
+      </c>
+      <c r="AA19">
+        <v>0.5</v>
+      </c>
+      <c r="AB19">
+        <v>1.87965595722198</v>
+      </c>
+      <c r="AC19">
+        <v>1.76343929767609</v>
+      </c>
+      <c r="AD19">
         <v>12.6120166809848</v>
       </c>
-      <c r="F19">
+      <c r="AE19">
+        <v>86677706696.70641</v>
+      </c>
+      <c r="AF19">
+        <v>1.59591357331042</v>
+      </c>
+      <c r="AG19">
+        <v>65.1010608504649</v>
+      </c>
+      <c r="AH19">
         <v>6.426</v>
       </c>
+      <c r="AI19">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="AJ19">
+        <v>1.47808432579041</v>
+      </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:36">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
+        <v>4.78625179421219</v>
+      </c>
+      <c r="D20">
+        <v>0.505214192405336</v>
+      </c>
+      <c r="E20">
+        <v>1.79020822048187</v>
+      </c>
+      <c r="F20">
+        <v>-2.38507161087906</v>
+      </c>
+      <c r="G20">
+        <v>53.1515356456582</v>
+      </c>
+      <c r="I20">
+        <v>32.3254037264858</v>
+      </c>
+      <c r="J20">
         <v>2.74296344906655</v>
       </c>
-      <c r="C20">
+      <c r="K20">
+        <v>49982.5999118346</v>
+      </c>
+      <c r="L20">
+        <v>46539.1761570405</v>
+      </c>
+      <c r="M20">
+        <v>1.28092659672814</v>
+      </c>
+      <c r="N20">
+        <v>32.5</v>
+      </c>
+      <c r="O20">
+        <v>1.67513394355774</v>
+      </c>
+      <c r="P20">
+        <v>20.6814326967462</v>
+      </c>
+      <c r="Q20">
+        <v>17.5409004540917</v>
+      </c>
+      <c r="R20">
+        <v>18.5291939067985</v>
+      </c>
+      <c r="S20">
+        <v>34.2744821243903</v>
+      </c>
+      <c r="T20">
         <v>2.26822567248104</v>
       </c>
-      <c r="D20">
+      <c r="U20">
         <v>6.28625779980977</v>
       </c>
-      <c r="E20">
+      <c r="V20">
+        <v>81.8087804878049</v>
+      </c>
+      <c r="W20">
+        <v>1.3176781061648</v>
+      </c>
+      <c r="X20">
+        <v>0.890962538332993</v>
+      </c>
+      <c r="Y20">
+        <v>0.9639710783958439</v>
+      </c>
+      <c r="Z20">
+        <v>37072620</v>
+      </c>
+      <c r="AA20">
+        <v>0.2</v>
+      </c>
+      <c r="AB20">
+        <v>1.69941985607147</v>
+      </c>
+      <c r="AC20">
+        <v>1.71514165401459</v>
+      </c>
+      <c r="AD20">
         <v>13.0576846693075</v>
       </c>
-      <c r="F20">
+      <c r="AE20">
+        <v>83925602808.00819</v>
+      </c>
+      <c r="AF20">
+        <v>1.43503478148261</v>
+      </c>
+      <c r="AG20">
+        <v>66.59988585087621</v>
+      </c>
+      <c r="AH20">
         <v>5.837</v>
       </c>
+      <c r="AI20">
+        <v>81.411</v>
+      </c>
+      <c r="AJ20">
+        <v>1.50241100788116</v>
+      </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:36">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
+        <v>4.70198129157197</v>
+      </c>
+      <c r="D21">
+        <v>0.503405461160356</v>
+      </c>
+      <c r="E21">
+        <v>1.72989678382874</v>
+      </c>
+      <c r="F21">
+        <v>-1.9517027481858</v>
+      </c>
+      <c r="G21">
+        <v>53.3623246913959</v>
+      </c>
+      <c r="I21">
+        <v>32.3526958202565</v>
+      </c>
+      <c r="J21">
         <v>1.90843194590616</v>
       </c>
-      <c r="C21">
+      <c r="K21">
+        <v>50498.9731057448</v>
+      </c>
+      <c r="L21">
+        <v>46352.8693445211</v>
+      </c>
+      <c r="M21">
+        <v>0.429657601305934</v>
+      </c>
+      <c r="N21">
+        <v>31.7</v>
+      </c>
+      <c r="O21">
+        <v>1.69731068611145</v>
+      </c>
+      <c r="P21">
+        <v>20.6634960880685</v>
+      </c>
+      <c r="Q21">
+        <v>18.1057096781026</v>
+      </c>
+      <c r="R21">
+        <v>18.2776090385263</v>
+      </c>
+      <c r="S21">
+        <v>33.8187894602395</v>
+      </c>
+      <c r="T21">
         <v>1.94926902411596</v>
       </c>
-      <c r="D21">
+      <c r="U21">
         <v>6.16490843592663</v>
       </c>
-      <c r="E21">
+      <c r="V21">
+        <v>82.1636585365854</v>
+      </c>
+      <c r="W21">
+        <v>1.28451224366918</v>
+      </c>
+      <c r="X21">
+        <v>0.238247240295596</v>
+      </c>
+      <c r="Y21">
+        <v>0.994933545589447</v>
+      </c>
+      <c r="Z21">
+        <v>37618495</v>
+      </c>
+      <c r="AA21">
+        <v>0.2</v>
+      </c>
+      <c r="AB21">
+        <v>1.71000242233276</v>
+      </c>
+      <c r="AC21">
+        <v>1.71977615356445</v>
+      </c>
+      <c r="AD21">
         <v>12.7416889014909</v>
       </c>
-      <c r="F21">
+      <c r="AE21">
+        <v>85297110783.68871</v>
+      </c>
+      <c r="AF21">
+        <v>1.44775879309167</v>
+      </c>
+      <c r="AG21">
+        <v>66.1714852804959</v>
+      </c>
+      <c r="AH21">
         <v>5.69</v>
       </c>
+      <c r="AI21">
+        <v>81.482</v>
+      </c>
+      <c r="AJ21">
+        <v>1.43030834197998</v>
+      </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:36">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
+        <v>4.55592854369171</v>
+      </c>
+      <c r="D22">
+        <v>0.529013916915578</v>
+      </c>
+      <c r="E22">
+        <v>1.56571280956268</v>
+      </c>
+      <c r="F22">
+        <v>-2.01049352658992</v>
+      </c>
+      <c r="G22">
+        <v>74.55440737915249</v>
+      </c>
+      <c r="I22">
+        <v>29.4736472349344</v>
+      </c>
+      <c r="J22">
         <v>-5.03823343468899</v>
       </c>
-      <c r="C22">
+      <c r="K22">
+        <v>48590.6832121939</v>
+      </c>
+      <c r="L22">
+        <v>43537.839298904</v>
+      </c>
+      <c r="M22">
+        <v>-6.06240642306676</v>
+      </c>
+      <c r="N22">
+        <v>29.9</v>
+      </c>
+      <c r="O22">
+        <v>1.59831285476685</v>
+      </c>
+      <c r="P22">
+        <v>22.7011077555498</v>
+      </c>
+      <c r="Q22">
+        <v>28.5714736058033</v>
+      </c>
+      <c r="R22">
+        <v>18.9901852083695</v>
+      </c>
+      <c r="S22">
+        <v>31.6831237283418</v>
+      </c>
+      <c r="T22">
         <v>0.7169996323078071</v>
       </c>
-      <c r="D22">
+      <c r="U22">
         <v>3.67774893330622</v>
       </c>
-      <c r="E22">
+      <c r="V22">
+        <v>81.53512195121949</v>
+      </c>
+      <c r="W22">
+        <v>1.40083568623706</v>
+      </c>
+      <c r="X22">
+        <v>-9.53931636017772</v>
+      </c>
+      <c r="Y22">
+        <v>1.01318228244781</v>
+      </c>
+      <c r="Z22">
+        <v>38028638</v>
+      </c>
+      <c r="AA22">
+        <v>0.2</v>
+      </c>
+      <c r="AB22">
+        <v>1.5925897359848</v>
+      </c>
+      <c r="AC22">
+        <v>1.61910331249237</v>
+      </c>
+      <c r="AD22">
         <v>13.5185987464231</v>
       </c>
-      <c r="F22">
+      <c r="AE22">
+        <v>90428136419.3486</v>
+      </c>
+      <c r="AF22">
+        <v>1.76069410604191</v>
+      </c>
+      <c r="AG22">
+        <v>61.1567709632763</v>
+      </c>
+      <c r="AH22">
         <v>9.657</v>
       </c>
+      <c r="AI22">
+        <v>81.562</v>
+      </c>
+      <c r="AJ22">
+        <v>1.47166883945465</v>
+      </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:36">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
+        <v>4.76800178849198</v>
+      </c>
+      <c r="D23">
+        <v>0.37810794618724</v>
+      </c>
+      <c r="E23">
+        <v>1.61626875400543</v>
+      </c>
+      <c r="F23">
+        <v>-0.0219632282728957</v>
+      </c>
+      <c r="G23">
+        <v>68.7795713723483</v>
+      </c>
+      <c r="I23">
+        <v>31.1750782983294</v>
+      </c>
+      <c r="J23">
         <v>5.95052802804381</v>
       </c>
-      <c r="C23">
+      <c r="K23">
+        <v>56995.1176781351</v>
+      </c>
+      <c r="L23">
+        <v>52886.6616372703</v>
+      </c>
+      <c r="M23">
+        <v>5.36528781293082</v>
+      </c>
+      <c r="N23">
+        <v>31.1</v>
+      </c>
+      <c r="O23">
+        <v>1.5614572763443</v>
+      </c>
+      <c r="P23">
+        <v>21.2842897783513</v>
+      </c>
+      <c r="Q23">
+        <v>22.4985744222565</v>
+      </c>
+      <c r="R23">
+        <v>19.862379496288</v>
+      </c>
+      <c r="S23">
+        <v>31.0717584176126</v>
+      </c>
+      <c r="T23">
         <v>3.39519318527533</v>
       </c>
-      <c r="D23">
+      <c r="U23">
         <v>4.4038617266293</v>
       </c>
-      <c r="E23">
+      <c r="V23">
+        <v>81.5168292682927</v>
+      </c>
+      <c r="W23">
+        <v>1.26729446473527</v>
+      </c>
+      <c r="X23">
+        <v>-2.40861514290875</v>
+      </c>
+      <c r="Y23">
+        <v>0.962336957454681</v>
+      </c>
+      <c r="Z23">
+        <v>38239864</v>
+      </c>
+      <c r="AA23">
+        <v>0.2</v>
+      </c>
+      <c r="AB23">
+        <v>1.61376404762268</v>
+      </c>
+      <c r="AC23">
+        <v>1.59289026260376</v>
+      </c>
+      <c r="AD23">
         <v>13.996294680919</v>
       </c>
-      <c r="F23">
+      <c r="AE23">
+        <v>106615119570.101</v>
+      </c>
+      <c r="AF23">
+        <v>1.72003903449133</v>
+      </c>
+      <c r="AG23">
+        <v>62.2468367159421</v>
+      </c>
+      <c r="AH23">
         <v>7.527</v>
       </c>
+      <c r="AI23">
+        <v>81.65300000000001</v>
+      </c>
+      <c r="AJ23">
+        <v>1.44535887241364</v>
+      </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:36">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
+        <v>4.87403846766279</v>
+      </c>
+      <c r="D24">
+        <v>0.342610204744156</v>
+      </c>
+      <c r="E24">
+        <v>1.65857303142548</v>
+      </c>
+      <c r="F24">
+        <v>-0.288416485092606</v>
+      </c>
+      <c r="G24">
+        <v>59.9440184640855</v>
+      </c>
+      <c r="I24">
+        <v>33.9431906669379</v>
+      </c>
+      <c r="J24">
         <v>4.18903628100851</v>
       </c>
-      <c r="C24">
+      <c r="K24">
+        <v>63578.3201949554</v>
+      </c>
+      <c r="L24">
+        <v>56256.8007264015</v>
+      </c>
+      <c r="M24">
+        <v>2.32641594463436</v>
+      </c>
+      <c r="O24">
+        <v>1.56661772727966</v>
+      </c>
+      <c r="P24">
+        <v>20.4184233971953</v>
+      </c>
+      <c r="Q24">
+        <v>18.2522606578883</v>
+      </c>
+      <c r="R24">
+        <v>18.9723038717055</v>
+      </c>
+      <c r="S24">
+        <v>33.374430889461</v>
+      </c>
+      <c r="T24">
         <v>6.80280115341609</v>
       </c>
-      <c r="D24">
+      <c r="U24">
         <v>6.04330455203215</v>
       </c>
-      <c r="E24">
+      <c r="V24">
+        <v>81.2453658536585</v>
+      </c>
+      <c r="W24">
+        <v>1.19577775821206</v>
+      </c>
+      <c r="X24">
+        <v>0.561814699713077</v>
+      </c>
+      <c r="Y24">
+        <v>0.780681550502777</v>
+      </c>
+      <c r="Z24">
+        <v>38935934</v>
+      </c>
+      <c r="AB24">
+        <v>1.67709279060364</v>
+      </c>
+      <c r="AC24">
+        <v>1.56462013721466</v>
+      </c>
+      <c r="AD24">
         <v>13.736451836938</v>
       </c>
-      <c r="F24">
+      <c r="AE24">
+        <v>106952377364.743</v>
+      </c>
+      <c r="AF24">
+        <v>1.46776084961637</v>
+      </c>
+      <c r="AG24">
+        <v>67.3176215563989</v>
+      </c>
+      <c r="AH24">
         <v>5.279</v>
       </c>
+      <c r="AI24">
+        <v>81.752</v>
+      </c>
+      <c r="AJ24">
+        <v>1.44002974033356</v>
+      </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:36">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
+        <v>4.74965858118068</v>
+      </c>
+      <c r="D25">
+        <v>0.456404574333028</v>
+      </c>
+      <c r="E25">
+        <v>1.67150104045868</v>
+      </c>
+      <c r="F25">
+        <v>-0.6333198985445589</v>
+      </c>
+      <c r="G25">
+        <v>62.4731322069255</v>
+      </c>
+      <c r="I25">
+        <v>33.3498760996793</v>
+      </c>
+      <c r="J25">
         <v>1.52874550838358</v>
       </c>
-      <c r="C25">
+      <c r="K25">
+        <v>64462.9211694495</v>
+      </c>
+      <c r="L25">
+        <v>54220.3285039875</v>
+      </c>
+      <c r="M25">
+        <v>-1.37792078609685</v>
+      </c>
+      <c r="O25">
+        <v>1.51680326461792</v>
+      </c>
+      <c r="P25">
+        <v>20.9054437744776</v>
+      </c>
+      <c r="Q25">
+        <v>19.2603133808938</v>
+      </c>
+      <c r="R25">
+        <v>20.0017383538811</v>
+      </c>
+      <c r="S25">
+        <v>33.2824552373876</v>
+      </c>
+      <c r="T25">
         <v>3.87900159788427</v>
       </c>
-      <c r="D25">
+      <c r="U25">
         <v>7.61422218132202</v>
       </c>
-      <c r="E25">
+      <c r="V25">
+        <v>81.6465853658537</v>
+      </c>
+      <c r="W25">
+        <v>1.29300145446276</v>
+      </c>
+      <c r="X25">
+        <v>0.800767602537315</v>
+      </c>
+      <c r="Y25">
+        <v>0.822420537471771</v>
+      </c>
+      <c r="Z25">
+        <v>40083484</v>
+      </c>
+      <c r="AB25">
+        <v>1.64471042156219</v>
+      </c>
+      <c r="AC25">
+        <v>1.47300565242767</v>
+      </c>
+      <c r="AD25">
         <v>14.089801316377</v>
       </c>
-      <c r="F25">
+      <c r="AE25">
+        <v>117550899244.64</v>
+      </c>
+      <c r="AF25">
+        <v>1.57415306335661</v>
+      </c>
+      <c r="AG25">
+        <v>66.6323313370668</v>
+      </c>
+      <c r="AH25">
         <v>5.415</v>
       </c>
+      <c r="AI25">
+        <v>81.86199999999999</v>
+      </c>
+      <c r="AJ25">
+        <v>1.4796462059021</v>
+      </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:36">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26">
+      <c r="F26">
+        <v>-0.461744367419551</v>
+      </c>
+      <c r="G26">
+        <v>64.9693295910634</v>
+      </c>
+      <c r="I26">
+        <v>32.4613353439237</v>
+      </c>
+      <c r="J26">
         <v>1.5280811085284</v>
       </c>
-      <c r="C26">
+      <c r="K26">
+        <v>65463.0990993361</v>
+      </c>
+      <c r="L26">
+        <v>54282.6176051733</v>
+      </c>
+      <c r="M26">
+        <v>-1.43527963580455</v>
+      </c>
+      <c r="R26">
+        <v>20.5369879331996</v>
+      </c>
+      <c r="S26">
+        <v>32.717698647348</v>
+      </c>
+      <c r="T26">
         <v>2.38158383281171</v>
       </c>
-      <c r="E26">
+      <c r="X26">
+        <v>-0.828162949051215</v>
+      </c>
+      <c r="Z26">
+        <v>41288599</v>
+      </c>
+      <c r="AD26">
         <v>14.2453671814569</v>
       </c>
-      <c r="F26">
+      <c r="AE26">
+        <v>119778473396.958</v>
+      </c>
+      <c r="AF26">
+        <v>1.56768935440642</v>
+      </c>
+      <c r="AG26">
+        <v>65.17903399127169</v>
+      </c>
+      <c r="AH26">
         <v>6.45</v>
+      </c>
+      <c r="AI26">
+        <v>81.98</v>
       </c>
     </row>
   </sheetData>
